--- a/artfynd/S 501-2026 artfynd.xlsx
+++ b/artfynd/S 501-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Hälsinglands flora (2019)</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84890531</t>
         </is>
       </c>
     </row>
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104939646</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121149360</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118676839</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106039275</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135058918</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106039135</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1497,6 +1537,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106038934</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1595,6 +1640,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106038743</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1698,6 +1748,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106038817</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1796,6 +1851,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106039276</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1899,6 +1959,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106038994</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1997,8 +2062,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106039183</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 501-2026 artfynd.xlsx
+++ b/artfynd/S 501-2026 artfynd.xlsx
@@ -1231,7 +1231,7 @@
         <v>135058918</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/S 501-2026 artfynd.xlsx
+++ b/artfynd/S 501-2026 artfynd.xlsx
@@ -1231,7 +1231,7 @@
         <v>135058918</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
